--- a/apps/api/assets/vocabulary/小学/人教版/五年级上.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/五年级上.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D134"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1117,6 +1117,16 @@
           <t>wash my clothes</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 洗我的衣服；洗衣服</t>
@@ -1151,6 +1161,16 @@
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>watch TV</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1192,6 +1212,16 @@
           <t>do homework</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 做作业；做家庭作业；做功课</t>
@@ -1230,6 +1260,16 @@
           <t>read books</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 读书；看书；阅读</t>
@@ -1265,6 +1305,16 @@
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>play football</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1399,6 +1449,16 @@
           <t>play sports</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 做运动；进行体育运动；进行体育活动</t>
@@ -1928,6 +1988,16 @@
           <t>sing English songs</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1940,6 +2010,16 @@
           <t>play the pipa</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1974,6 +2054,16 @@
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>do kung fu</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2063,6 +2153,16 @@
           <t>draw cartoons</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -2125,6 +2225,16 @@
           <t>play basketball</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 打篮球；玩篮球；篮球锻炼知多少</t>
@@ -2159,6 +2269,16 @@
           <t>play ping-pong</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 打乒乓球</t>
@@ -2171,6 +2291,16 @@
           <t>speak English</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 说英语；讲英语；相信我会讲英文</t>
@@ -2183,6 +2313,16 @@
           <t>we'll</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t>abbr. 我们将（we shall，we will）</t>
@@ -2193,6 +2333,16 @@
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>we will</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2348,6 +2498,16 @@
           <t>no problem</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 没问题
@@ -2530,6 +2690,16 @@
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>water bottle</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -2855,6 +3025,16 @@
           <t>lots of</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 许多；很多
@@ -3297,6 +3477,16 @@
           <t>go boating</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 乘船〔尤指划船〕游玩
@@ -3310,6 +3500,16 @@
           <t>aren't</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
           <t>abbr. 不是（are not）</t>
@@ -3320,6 +3520,16 @@
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>are not</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
